--- a/00.WBS/03. WBS 상세 (기술 레이어별 일정표).xlsx
+++ b/00.WBS/03. WBS 상세 (기술 레이어별 일정표).xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nklee\Desktop\OBSIDIAN_v2\04.MS-DataSchool\20.PROJECT\22.MS_2nd_Project\00.MS_2nd_Project_PM\00.WBS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nklee\Desktop\OBSIDIAN_v2\04.MS-DataSchool\20.PROJECT\22.MS_2nd_Project\01.MS_2nd_Project_Team\00.WBS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDE96CDD-DD53-47B0-A579-E60ED9E21D0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B401CCFD-AB79-4C00-B9C6-E2FE476D011E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1884" yWindow="0" windowWidth="12192" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12684" yWindow="480" windowWidth="10200" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WBS" sheetId="1" r:id="rId1"/>
@@ -584,7 +584,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -648,6 +648,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="25">
     <border>
@@ -985,7 +991,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1081,18 +1087,6 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1279,6 +1273,42 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1598,38 +1628,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
+      <c r="H1" s="93"/>
+      <c r="I1" s="93"/>
+      <c r="J1" s="93"/>
+      <c r="K1" s="93"/>
+      <c r="L1" s="93"/>
+      <c r="M1" s="93"/>
+      <c r="N1" s="93"/>
+      <c r="O1" s="93"/>
+      <c r="P1" s="93"/>
+      <c r="Q1" s="93"/>
+      <c r="R1" s="93"/>
+      <c r="S1" s="93"/>
+      <c r="T1" s="93"/>
+      <c r="U1" s="93"/>
+      <c r="V1" s="93"/>
+      <c r="W1" s="93"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="U2" s="96" t="s">
+      <c r="U2" s="92" t="s">
         <v>23</v>
       </c>
-      <c r="V2" s="97"/>
-      <c r="W2" s="97"/>
+      <c r="V2" s="93"/>
+      <c r="W2" s="93"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
@@ -1789,73 +1819,73 @@
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A9" s="61" t="s">
+      <c r="A9" s="57" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="62" t="s">
+      <c r="B9" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="62" t="s">
+      <c r="C9" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="62" t="s">
+      <c r="D9" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="E9" s="62" t="s">
+      <c r="E9" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="F9" s="62" t="s">
+      <c r="F9" s="58" t="s">
         <v>59</v>
       </c>
-      <c r="G9" s="63">
+      <c r="G9" s="59">
         <v>1</v>
       </c>
-      <c r="H9" s="63">
+      <c r="H9" s="59">
         <v>2</v>
       </c>
-      <c r="I9" s="63">
+      <c r="I9" s="59">
         <v>3</v>
       </c>
-      <c r="J9" s="64">
+      <c r="J9" s="60">
         <v>4</v>
       </c>
-      <c r="K9" s="65">
+      <c r="K9" s="61">
         <v>5</v>
       </c>
-      <c r="L9" s="65">
+      <c r="L9" s="61">
         <v>6</v>
       </c>
-      <c r="M9" s="65">
+      <c r="M9" s="61">
         <v>7</v>
       </c>
-      <c r="N9" s="65">
+      <c r="N9" s="61">
         <v>8</v>
       </c>
-      <c r="O9" s="65">
+      <c r="O9" s="61">
         <v>9</v>
       </c>
-      <c r="P9" s="65">
+      <c r="P9" s="61">
         <v>10</v>
       </c>
-      <c r="Q9" s="64">
+      <c r="Q9" s="60">
         <v>11</v>
       </c>
-      <c r="R9" s="64">
+      <c r="R9" s="60">
         <v>12</v>
       </c>
-      <c r="S9" s="64">
+      <c r="S9" s="60">
         <v>13</v>
       </c>
-      <c r="T9" s="65">
+      <c r="T9" s="61">
         <v>14</v>
       </c>
-      <c r="U9" s="65">
+      <c r="U9" s="61">
         <v>15</v>
       </c>
-      <c r="V9" s="78">
+      <c r="V9" s="74">
         <v>16</v>
       </c>
-      <c r="W9" s="89" t="s">
+      <c r="W9" s="85" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1863,42 +1893,42 @@
       <c r="A10" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="96" t="s">
         <v>61</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="97" t="s">
         <v>62</v>
       </c>
-      <c r="D10" s="35" t="s">
+      <c r="D10" s="98" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="36" t="str">
+      <c r="E10" s="99" t="str">
         <f t="shared" ref="E10:E16" si="0">$B$3</f>
         <v>최민</v>
       </c>
-      <c r="F10" s="37" t="s">
+      <c r="F10" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="G10" s="38"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="38"/>
-      <c r="J10" s="38"/>
-      <c r="K10" s="38"/>
-      <c r="L10" s="38"/>
-      <c r="M10" s="38"/>
-      <c r="N10" s="38"/>
-      <c r="O10" s="38"/>
-      <c r="P10" s="38"/>
-      <c r="Q10" s="39"/>
-      <c r="R10" s="39"/>
-      <c r="S10" s="39"/>
-      <c r="T10" s="39"/>
-      <c r="U10" s="39"/>
-      <c r="V10" s="79"/>
-      <c r="W10" s="90"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="34"/>
+      <c r="J10" s="34"/>
+      <c r="K10" s="34"/>
+      <c r="L10" s="34"/>
+      <c r="M10" s="34"/>
+      <c r="N10" s="34"/>
+      <c r="O10" s="34"/>
+      <c r="P10" s="34"/>
+      <c r="Q10" s="35"/>
+      <c r="R10" s="35"/>
+      <c r="S10" s="35"/>
+      <c r="T10" s="35"/>
+      <c r="U10" s="35"/>
+      <c r="V10" s="75"/>
+      <c r="W10" s="86"/>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A11" s="40" t="s">
+      <c r="A11" s="36" t="s">
         <v>24</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -1932,11 +1962,11 @@
       <c r="S11" s="14"/>
       <c r="T11" s="13"/>
       <c r="U11" s="13"/>
-      <c r="V11" s="80"/>
-      <c r="W11" s="91"/>
+      <c r="V11" s="76"/>
+      <c r="W11" s="87"/>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A12" s="40" t="s">
+      <c r="A12" s="36" t="s">
         <v>24</v>
       </c>
       <c r="B12" s="8" t="s">
@@ -1970,23 +2000,23 @@
       <c r="S12" s="13"/>
       <c r="T12" s="14"/>
       <c r="U12" s="14"/>
-      <c r="V12" s="81"/>
-      <c r="W12" s="91"/>
+      <c r="V12" s="77"/>
+      <c r="W12" s="87"/>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A13" s="40" t="s">
+      <c r="A13" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="100" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="101" t="s">
         <v>71</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="E13" s="11" t="str">
+      <c r="E13" s="103" t="str">
         <f t="shared" si="0"/>
         <v>최민</v>
       </c>
@@ -2008,23 +2038,23 @@
       <c r="S13" s="13"/>
       <c r="T13" s="13"/>
       <c r="U13" s="13"/>
-      <c r="V13" s="80"/>
-      <c r="W13" s="91"/>
+      <c r="V13" s="76"/>
+      <c r="W13" s="87"/>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A14" s="40" t="s">
+      <c r="A14" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="100" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="101" t="s">
         <v>74</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="102" t="s">
         <v>75</v>
       </c>
-      <c r="E14" s="11" t="str">
+      <c r="E14" s="103" t="str">
         <f t="shared" si="0"/>
         <v>최민</v>
       </c>
@@ -2046,11 +2076,11 @@
       <c r="S14" s="13"/>
       <c r="T14" s="13"/>
       <c r="U14" s="13"/>
-      <c r="V14" s="80"/>
-      <c r="W14" s="91"/>
+      <c r="V14" s="76"/>
+      <c r="W14" s="87"/>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A15" s="40" t="s">
+      <c r="A15" s="36" t="s">
         <v>24</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -2084,61 +2114,61 @@
       <c r="S15" s="14"/>
       <c r="T15" s="13"/>
       <c r="U15" s="13"/>
-      <c r="V15" s="80"/>
-      <c r="W15" s="91"/>
+      <c r="V15" s="76"/>
+      <c r="W15" s="87"/>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A16" s="41" t="s">
+      <c r="A16" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="42" t="s">
+      <c r="B16" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="C16" s="43" t="s">
+      <c r="C16" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="D16" s="44" t="s">
+      <c r="D16" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="E16" s="45" t="str">
+      <c r="E16" s="41" t="str">
         <f t="shared" si="0"/>
         <v>최민</v>
       </c>
-      <c r="F16" s="46" t="s">
+      <c r="F16" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="G16" s="47"/>
-      <c r="H16" s="47"/>
-      <c r="I16" s="47"/>
-      <c r="J16" s="47"/>
-      <c r="K16" s="47"/>
-      <c r="L16" s="47"/>
-      <c r="M16" s="47"/>
-      <c r="N16" s="47"/>
-      <c r="O16" s="47"/>
-      <c r="P16" s="47"/>
-      <c r="Q16" s="47"/>
-      <c r="R16" s="47"/>
-      <c r="S16" s="47"/>
-      <c r="T16" s="48"/>
-      <c r="U16" s="48"/>
-      <c r="V16" s="82"/>
-      <c r="W16" s="92"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="43"/>
+      <c r="L16" s="43"/>
+      <c r="M16" s="43"/>
+      <c r="N16" s="43"/>
+      <c r="O16" s="43"/>
+      <c r="P16" s="43"/>
+      <c r="Q16" s="43"/>
+      <c r="R16" s="43"/>
+      <c r="S16" s="43"/>
+      <c r="T16" s="44"/>
+      <c r="U16" s="44"/>
+      <c r="V16" s="78"/>
+      <c r="W16" s="88"/>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A17" s="66" t="s">
+      <c r="A17" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="104" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="105" t="s">
         <v>81</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="106" t="s">
         <v>82</v>
       </c>
-      <c r="E17" s="28" t="str">
+      <c r="E17" s="107" t="str">
         <f>$B$4</f>
         <v>임현제</v>
       </c>
@@ -2160,11 +2190,11 @@
       <c r="S17" s="31"/>
       <c r="T17" s="31"/>
       <c r="U17" s="31"/>
-      <c r="V17" s="83"/>
-      <c r="W17" s="93"/>
+      <c r="V17" s="79"/>
+      <c r="W17" s="89"/>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A18" s="67" t="s">
+      <c r="A18" s="63" t="s">
         <v>26</v>
       </c>
       <c r="B18" s="8" t="s">
@@ -2198,11 +2228,11 @@
       <c r="S18" s="15"/>
       <c r="T18" s="13"/>
       <c r="U18" s="13"/>
-      <c r="V18" s="80"/>
-      <c r="W18" s="91"/>
+      <c r="V18" s="76"/>
+      <c r="W18" s="87"/>
     </row>
     <row r="19" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A19" s="67" t="s">
+      <c r="A19" s="63" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="8" t="s">
@@ -2236,87 +2266,87 @@
       <c r="S19" s="15"/>
       <c r="T19" s="13"/>
       <c r="U19" s="13"/>
-      <c r="V19" s="80"/>
-      <c r="W19" s="91"/>
+      <c r="V19" s="76"/>
+      <c r="W19" s="87"/>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A20" s="68" t="s">
+      <c r="A20" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="49" t="s">
+      <c r="B20" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="C20" s="50" t="s">
+      <c r="C20" s="46" t="s">
         <v>89</v>
       </c>
-      <c r="D20" s="51" t="s">
+      <c r="D20" s="47" t="s">
         <v>90</v>
       </c>
-      <c r="E20" s="52" t="str">
+      <c r="E20" s="48" t="str">
         <f>$B$4</f>
         <v>임현제</v>
       </c>
-      <c r="F20" s="53" t="s">
+      <c r="F20" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="G20" s="54"/>
-      <c r="H20" s="54"/>
-      <c r="I20" s="54"/>
-      <c r="J20" s="54"/>
-      <c r="K20" s="54"/>
-      <c r="L20" s="54"/>
-      <c r="M20" s="54"/>
-      <c r="N20" s="54"/>
-      <c r="O20" s="54"/>
-      <c r="P20" s="54"/>
-      <c r="Q20" s="54"/>
-      <c r="R20" s="54"/>
-      <c r="S20" s="54"/>
-      <c r="T20" s="55"/>
-      <c r="U20" s="55"/>
-      <c r="V20" s="84"/>
-      <c r="W20" s="94"/>
+      <c r="G20" s="50"/>
+      <c r="H20" s="50"/>
+      <c r="I20" s="50"/>
+      <c r="J20" s="50"/>
+      <c r="K20" s="50"/>
+      <c r="L20" s="50"/>
+      <c r="M20" s="50"/>
+      <c r="N20" s="50"/>
+      <c r="O20" s="50"/>
+      <c r="P20" s="50"/>
+      <c r="Q20" s="50"/>
+      <c r="R20" s="50"/>
+      <c r="S20" s="50"/>
+      <c r="T20" s="51"/>
+      <c r="U20" s="51"/>
+      <c r="V20" s="80"/>
+      <c r="W20" s="90"/>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A21" s="56" t="s">
+      <c r="A21" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="33" t="s">
+      <c r="B21" s="96" t="s">
         <v>91</v>
       </c>
-      <c r="C21" s="34" t="s">
+      <c r="C21" s="97" t="s">
         <v>92</v>
       </c>
-      <c r="D21" s="35" t="s">
+      <c r="D21" s="98" t="s">
         <v>93</v>
       </c>
-      <c r="E21" s="36" t="str">
+      <c r="E21" s="99" t="str">
         <f>$B$6</f>
         <v>임현제/최민/나경</v>
       </c>
-      <c r="F21" s="37" t="s">
+      <c r="F21" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="G21" s="57"/>
-      <c r="H21" s="57"/>
-      <c r="I21" s="57"/>
-      <c r="J21" s="57"/>
-      <c r="K21" s="57"/>
-      <c r="L21" s="57"/>
-      <c r="M21" s="57"/>
-      <c r="N21" s="57"/>
-      <c r="O21" s="57"/>
-      <c r="P21" s="57"/>
-      <c r="Q21" s="39"/>
-      <c r="R21" s="39"/>
-      <c r="S21" s="39"/>
-      <c r="T21" s="39"/>
-      <c r="U21" s="39"/>
-      <c r="V21" s="79"/>
-      <c r="W21" s="90"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="53"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="53"/>
+      <c r="L21" s="53"/>
+      <c r="M21" s="53"/>
+      <c r="N21" s="53"/>
+      <c r="O21" s="53"/>
+      <c r="P21" s="53"/>
+      <c r="Q21" s="35"/>
+      <c r="R21" s="35"/>
+      <c r="S21" s="35"/>
+      <c r="T21" s="35"/>
+      <c r="U21" s="35"/>
+      <c r="V21" s="75"/>
+      <c r="W21" s="86"/>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A22" s="58" t="s">
+      <c r="A22" s="54" t="s">
         <v>28</v>
       </c>
       <c r="B22" s="8" t="s">
@@ -2350,87 +2380,87 @@
       <c r="S22" s="16"/>
       <c r="T22" s="13"/>
       <c r="U22" s="13"/>
-      <c r="V22" s="80"/>
-      <c r="W22" s="91"/>
+      <c r="V22" s="76"/>
+      <c r="W22" s="87"/>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A23" s="59" t="s">
+      <c r="A23" s="55" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="42" t="s">
+      <c r="B23" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="C23" s="43" t="s">
+      <c r="C23" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="44" t="s">
+      <c r="D23" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="E23" s="45" t="str">
+      <c r="E23" s="41" t="str">
         <f>$B$6</f>
         <v>임현제/최민/나경</v>
       </c>
-      <c r="F23" s="46" t="s">
+      <c r="F23" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="G23" s="47"/>
-      <c r="H23" s="47"/>
-      <c r="I23" s="47"/>
-      <c r="J23" s="47"/>
-      <c r="K23" s="47"/>
-      <c r="L23" s="47"/>
-      <c r="M23" s="47"/>
-      <c r="N23" s="47"/>
-      <c r="O23" s="47"/>
-      <c r="P23" s="47"/>
-      <c r="Q23" s="47"/>
-      <c r="R23" s="47"/>
-      <c r="S23" s="47"/>
-      <c r="T23" s="60"/>
-      <c r="U23" s="60"/>
-      <c r="V23" s="85"/>
-      <c r="W23" s="92"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="43"/>
+      <c r="L23" s="43"/>
+      <c r="M23" s="43"/>
+      <c r="N23" s="43"/>
+      <c r="O23" s="43"/>
+      <c r="P23" s="43"/>
+      <c r="Q23" s="43"/>
+      <c r="R23" s="43"/>
+      <c r="S23" s="43"/>
+      <c r="T23" s="56"/>
+      <c r="U23" s="56"/>
+      <c r="V23" s="81"/>
+      <c r="W23" s="88"/>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A24" s="74" t="s">
+      <c r="A24" s="70" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="33" t="s">
+      <c r="B24" s="96" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="34" t="s">
+      <c r="C24" s="97" t="s">
         <v>99</v>
       </c>
-      <c r="D24" s="35" t="s">
+      <c r="D24" s="98" t="s">
         <v>100</v>
       </c>
-      <c r="E24" s="36" t="str">
+      <c r="E24" s="99" t="str">
         <f>$B$7</f>
         <v>박형준</v>
       </c>
-      <c r="F24" s="37" t="s">
+      <c r="F24" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="G24" s="75"/>
-      <c r="H24" s="75"/>
-      <c r="I24" s="75"/>
-      <c r="J24" s="75"/>
-      <c r="K24" s="75"/>
-      <c r="L24" s="75"/>
-      <c r="M24" s="75"/>
-      <c r="N24" s="75"/>
-      <c r="O24" s="75"/>
-      <c r="P24" s="75"/>
-      <c r="Q24" s="39"/>
-      <c r="R24" s="39"/>
-      <c r="S24" s="39"/>
-      <c r="T24" s="39"/>
-      <c r="U24" s="39"/>
-      <c r="V24" s="79"/>
-      <c r="W24" s="90"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="71"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="71"/>
+      <c r="L24" s="71"/>
+      <c r="M24" s="71"/>
+      <c r="N24" s="71"/>
+      <c r="O24" s="71"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="35"/>
+      <c r="R24" s="35"/>
+      <c r="S24" s="35"/>
+      <c r="T24" s="35"/>
+      <c r="U24" s="35"/>
+      <c r="V24" s="75"/>
+      <c r="W24" s="86"/>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A25" s="69" t="s">
+      <c r="A25" s="65" t="s">
         <v>29</v>
       </c>
       <c r="B25" s="8" t="s">
@@ -2464,11 +2494,11 @@
       <c r="S25" s="17"/>
       <c r="T25" s="13"/>
       <c r="U25" s="13"/>
-      <c r="V25" s="80"/>
-      <c r="W25" s="91"/>
+      <c r="V25" s="76"/>
+      <c r="W25" s="87"/>
     </row>
     <row r="26" spans="1:23" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="69" t="s">
+      <c r="A26" s="65" t="s">
         <v>29</v>
       </c>
       <c r="B26" s="8" t="s">
@@ -2502,49 +2532,49 @@
       <c r="S26" s="13"/>
       <c r="T26" s="17"/>
       <c r="U26" s="17"/>
-      <c r="V26" s="86"/>
-      <c r="W26" s="91"/>
+      <c r="V26" s="82"/>
+      <c r="W26" s="87"/>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A27" s="76" t="s">
+      <c r="A27" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="42" t="s">
+      <c r="B27" s="38" t="s">
         <v>106</v>
       </c>
-      <c r="C27" s="43" t="s">
+      <c r="C27" s="39" t="s">
         <v>107</v>
       </c>
-      <c r="D27" s="44" t="s">
+      <c r="D27" s="40" t="s">
         <v>108</v>
       </c>
-      <c r="E27" s="45" t="str">
+      <c r="E27" s="41" t="str">
         <f>$B$7</f>
         <v>박형준</v>
       </c>
-      <c r="F27" s="46" t="s">
+      <c r="F27" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="G27" s="47"/>
-      <c r="H27" s="47"/>
-      <c r="I27" s="47"/>
-      <c r="J27" s="47"/>
-      <c r="K27" s="47"/>
-      <c r="L27" s="47"/>
-      <c r="M27" s="47"/>
-      <c r="N27" s="47"/>
-      <c r="O27" s="47"/>
-      <c r="P27" s="47"/>
-      <c r="Q27" s="47"/>
-      <c r="R27" s="47"/>
-      <c r="S27" s="47"/>
-      <c r="T27" s="77"/>
-      <c r="U27" s="77"/>
-      <c r="V27" s="87"/>
-      <c r="W27" s="92"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="43"/>
+      <c r="K27" s="43"/>
+      <c r="L27" s="43"/>
+      <c r="M27" s="43"/>
+      <c r="N27" s="43"/>
+      <c r="O27" s="43"/>
+      <c r="P27" s="43"/>
+      <c r="Q27" s="43"/>
+      <c r="R27" s="43"/>
+      <c r="S27" s="43"/>
+      <c r="T27" s="73"/>
+      <c r="U27" s="73"/>
+      <c r="V27" s="83"/>
+      <c r="W27" s="88"/>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A28" s="72" t="s">
+      <c r="A28" s="68" t="s">
         <v>109</v>
       </c>
       <c r="B28" s="25" t="s">
@@ -2571,17 +2601,17 @@
       <c r="M28" s="31"/>
       <c r="N28" s="31"/>
       <c r="O28" s="31"/>
-      <c r="P28" s="73"/>
+      <c r="P28" s="69"/>
       <c r="Q28" s="31"/>
       <c r="R28" s="31"/>
       <c r="S28" s="31"/>
       <c r="T28" s="31"/>
       <c r="U28" s="31"/>
-      <c r="V28" s="83"/>
-      <c r="W28" s="93"/>
+      <c r="V28" s="79"/>
+      <c r="W28" s="89"/>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A29" s="70" t="s">
+      <c r="A29" s="66" t="s">
         <v>109</v>
       </c>
       <c r="B29" s="8" t="s">
@@ -2614,70 +2644,70 @@
       <c r="S29" s="18"/>
       <c r="T29" s="13"/>
       <c r="U29" s="13"/>
-      <c r="V29" s="80"/>
-      <c r="W29" s="91"/>
+      <c r="V29" s="76"/>
+      <c r="W29" s="87"/>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A30" s="71" t="s">
+      <c r="A30" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="B30" s="42" t="s">
+      <c r="B30" s="38" t="s">
         <v>116</v>
       </c>
-      <c r="C30" s="43" t="s">
+      <c r="C30" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="D30" s="44" t="s">
+      <c r="D30" s="40" t="s">
         <v>118</v>
       </c>
-      <c r="E30" s="45" t="s">
+      <c r="E30" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="F30" s="46" t="s">
+      <c r="F30" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="G30" s="47"/>
-      <c r="H30" s="47"/>
-      <c r="I30" s="47"/>
-      <c r="J30" s="47"/>
-      <c r="K30" s="47"/>
-      <c r="L30" s="47"/>
-      <c r="M30" s="47"/>
-      <c r="N30" s="47"/>
-      <c r="O30" s="47"/>
-      <c r="P30" s="47"/>
-      <c r="Q30" s="47"/>
-      <c r="R30" s="47"/>
-      <c r="S30" s="47"/>
-      <c r="T30" s="47"/>
-      <c r="U30" s="47"/>
-      <c r="V30" s="88"/>
-      <c r="W30" s="95"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
+      <c r="L30" s="43"/>
+      <c r="M30" s="43"/>
+      <c r="N30" s="43"/>
+      <c r="O30" s="43"/>
+      <c r="P30" s="43"/>
+      <c r="Q30" s="43"/>
+      <c r="R30" s="43"/>
+      <c r="S30" s="43"/>
+      <c r="T30" s="43"/>
+      <c r="U30" s="43"/>
+      <c r="V30" s="84"/>
+      <c r="W30" s="91"/>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A31" s="97"/>
-      <c r="B31" s="97"/>
-      <c r="C31" s="97"/>
-      <c r="D31" s="97"/>
-      <c r="E31" s="97"/>
-      <c r="F31" s="97"/>
-      <c r="G31" s="97"/>
-      <c r="H31" s="97"/>
-      <c r="I31" s="97"/>
-      <c r="J31" s="97"/>
-      <c r="K31" s="97"/>
-      <c r="L31" s="97"/>
-      <c r="M31" s="97"/>
-      <c r="N31" s="97"/>
-      <c r="O31" s="97"/>
-      <c r="P31" s="97"/>
-      <c r="Q31" s="97"/>
-      <c r="R31" s="97"/>
-      <c r="S31" s="97"/>
-      <c r="T31" s="97"/>
-      <c r="U31" s="97"/>
-      <c r="V31" s="97"/>
-      <c r="W31" s="97"/>
+      <c r="A31" s="93"/>
+      <c r="B31" s="93"/>
+      <c r="C31" s="93"/>
+      <c r="D31" s="93"/>
+      <c r="E31" s="93"/>
+      <c r="F31" s="93"/>
+      <c r="G31" s="93"/>
+      <c r="H31" s="93"/>
+      <c r="I31" s="93"/>
+      <c r="J31" s="93"/>
+      <c r="K31" s="93"/>
+      <c r="L31" s="93"/>
+      <c r="M31" s="93"/>
+      <c r="N31" s="93"/>
+      <c r="O31" s="93"/>
+      <c r="P31" s="93"/>
+      <c r="Q31" s="93"/>
+      <c r="R31" s="93"/>
+      <c r="S31" s="93"/>
+      <c r="T31" s="93"/>
+      <c r="U31" s="93"/>
+      <c r="V31" s="93"/>
+      <c r="W31" s="93"/>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
@@ -2709,11 +2739,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="95" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
